--- a/artfynd/A 4615-2025 artfynd.xlsx
+++ b/artfynd/A 4615-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123445737</v>
+        <v>123445745</v>
       </c>
       <c r="B2" t="n">
-        <v>57634</v>
+        <v>57632</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>411017</v>
+        <v>410992</v>
       </c>
       <c r="R2" t="n">
-        <v>6239474</v>
+        <v>6239484</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -895,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123425822</v>
+        <v>123445741</v>
       </c>
       <c r="B4" t="n">
         <v>57851</v>
@@ -931,17 +931,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tidemanstorp, Tidemanstorp, Sk</t>
+          <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>410977</v>
+        <v>410991</v>
       </c>
       <c r="R4" t="n">
-        <v>6239502</v>
+        <v>6239508</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,19 +968,9 @@
           <t>2025-03-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,12 +985,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1251,7 +1241,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123445741</v>
+        <v>123425822</v>
       </c>
       <c r="B7" t="n">
         <v>57851</v>
@@ -1287,17 +1277,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fäje myr norr, Sk</t>
+          <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>410991</v>
+        <v>410977</v>
       </c>
       <c r="R7" t="n">
-        <v>6239508</v>
+        <v>6239502</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1324,9 +1314,19 @@
           <t>2025-03-24</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,22 +1341,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123445745</v>
+        <v>123445737</v>
       </c>
       <c r="B8" t="n">
-        <v>57632</v>
+        <v>57634</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,21 +1369,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>410992</v>
+        <v>411017</v>
       </c>
       <c r="R8" t="n">
-        <v>6239484</v>
+        <v>6239474</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>

--- a/artfynd/A 4615-2025 artfynd.xlsx
+++ b/artfynd/A 4615-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123445745</v>
+        <v>123427756</v>
       </c>
       <c r="B2" t="n">
-        <v>57632</v>
+        <v>56691</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,57 +687,51 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fäje myr norr, Sk</t>
+          <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>410992</v>
+        <v>410821</v>
       </c>
       <c r="R2" t="n">
-        <v>6239484</v>
+        <v>6239470</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,9 +758,24 @@
           <t>2025-03-24</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flög upp från träd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,22 +790,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123445744</v>
+        <v>123445745</v>
       </c>
       <c r="B3" t="n">
-        <v>58159</v>
+        <v>57632</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,20 +814,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -826,17 +835,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411000</v>
+        <v>410992</v>
       </c>
       <c r="R3" t="n">
-        <v>6239530</v>
+        <v>6239484</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -895,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123445741</v>
+        <v>123426658</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>57634</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,41 +932,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fäje myr norr, Sk</t>
+          <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>410991</v>
+        <v>410969</v>
       </c>
       <c r="R4" t="n">
-        <v>6239508</v>
+        <v>6239507</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -968,9 +998,19 @@
           <t>2025-03-24</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,22 +1025,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123427756</v>
+        <v>123445735</v>
       </c>
       <c r="B5" t="n">
-        <v>56691</v>
+        <v>57634</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,51 +1049,57 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>rastande</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tidemanstorp, Tidemanstorp, Sk</t>
+          <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>410821</v>
+        <v>411027</v>
       </c>
       <c r="R5" t="n">
-        <v>6239470</v>
+        <v>6239523</v>
       </c>
       <c r="S5" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,24 +1126,9 @@
           <t>2025-03-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flög upp från träd</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,22 +1143,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123426658</v>
+        <v>123445744</v>
       </c>
       <c r="B6" t="n">
-        <v>57634</v>
+        <v>58159</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,46 +1167,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>103044</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tidemanstorp, Tidemanstorp, Sk</t>
+          <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>410969</v>
+        <v>411000</v>
       </c>
       <c r="R6" t="n">
-        <v>6239507</v>
+        <v>6239530</v>
       </c>
       <c r="S6" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,19 +1228,9 @@
           <t>2025-03-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,12 +1245,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1353,10 +1369,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123445737</v>
+        <v>123445741</v>
       </c>
       <c r="B8" t="n">
-        <v>57634</v>
+        <v>57851</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,54 +1381,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>411017</v>
+        <v>410991</v>
       </c>
       <c r="R8" t="n">
-        <v>6239474</v>
+        <v>6239508</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1471,7 +1471,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123445735</v>
+        <v>123445737</v>
       </c>
       <c r="B9" t="n">
         <v>57634</v>
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>411027</v>
+        <v>411017</v>
       </c>
       <c r="R9" t="n">
-        <v>6239523</v>
+        <v>6239474</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 4615-2025 artfynd.xlsx
+++ b/artfynd/A 4615-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123445735</v>
+        <v>123427756</v>
       </c>
       <c r="B2" t="n">
-        <v>57634</v>
+        <v>56697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,57 +687,51 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fäje myr norr, Sk</t>
+          <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>411027</v>
+        <v>410821</v>
       </c>
       <c r="R2" t="n">
-        <v>6239523</v>
+        <v>6239470</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,9 +758,24 @@
           <t>2025-03-24</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flög upp från träd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,22 +790,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123445737</v>
+        <v>123445741</v>
       </c>
       <c r="B3" t="n">
-        <v>57634</v>
+        <v>57857</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,54 +814,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411017</v>
+        <v>410991</v>
       </c>
       <c r="R3" t="n">
-        <v>6239474</v>
+        <v>6239508</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -911,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123427756</v>
+        <v>123445745</v>
       </c>
       <c r="B4" t="n">
-        <v>56691</v>
+        <v>57638</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,51 +916,57 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>rastande</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tidemanstorp, Tidemanstorp, Sk</t>
+          <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>410821</v>
+        <v>410992</v>
       </c>
       <c r="R4" t="n">
-        <v>6239470</v>
+        <v>6239484</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,24 +993,9 @@
           <t>2025-03-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flög upp från träd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,22 +1010,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123445741</v>
+        <v>123425822</v>
       </c>
       <c r="B5" t="n">
-        <v>57851</v>
+        <v>57857</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1074,17 +1058,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fäje myr norr, Sk</t>
+          <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>410991</v>
+        <v>410977</v>
       </c>
       <c r="R5" t="n">
-        <v>6239508</v>
+        <v>6239502</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1111,9 +1095,19 @@
           <t>2025-03-24</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,22 +1122,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123445744</v>
+        <v>123426658</v>
       </c>
       <c r="B6" t="n">
-        <v>58159</v>
+        <v>57640</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,41 +1146,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fäje myr norr, Sk</t>
+          <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>411000</v>
+        <v>410969</v>
       </c>
       <c r="R6" t="n">
-        <v>6239530</v>
+        <v>6239507</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,9 +1212,19 @@
           <t>2025-03-24</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,22 +1239,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123426658</v>
+        <v>123445735</v>
       </c>
       <c r="B7" t="n">
-        <v>57634</v>
+        <v>57640</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,25 +1284,36 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tidemanstorp, Tidemanstorp, Sk</t>
+          <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>410969</v>
+        <v>411027</v>
       </c>
       <c r="R7" t="n">
-        <v>6239507</v>
+        <v>6239523</v>
       </c>
       <c r="S7" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1320,19 +1340,9 @@
           <t>2025-03-24</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,22 +1357,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123425822</v>
+        <v>123445744</v>
       </c>
       <c r="B8" t="n">
-        <v>57851</v>
+        <v>58165</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1375,16 +1385,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1395,17 +1405,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tidemanstorp, Tidemanstorp, Sk</t>
+          <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>410977</v>
+        <v>411000</v>
       </c>
       <c r="R8" t="n">
-        <v>6239502</v>
+        <v>6239530</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,19 +1442,9 @@
           <t>2025-03-24</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,22 +1459,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123445745</v>
+        <v>123445737</v>
       </c>
       <c r="B9" t="n">
-        <v>57632</v>
+        <v>57640</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>410992</v>
+        <v>411017</v>
       </c>
       <c r="R9" t="n">
-        <v>6239484</v>
+        <v>6239474</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 4615-2025 artfynd.xlsx
+++ b/artfynd/A 4615-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123427756</v>
+        <v>123445735</v>
       </c>
       <c r="B2" t="n">
-        <v>56697</v>
+        <v>57643</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,51 +687,57 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>rastande</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tidemanstorp, Tidemanstorp, Sk</t>
+          <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>410821</v>
+        <v>411027</v>
       </c>
       <c r="R2" t="n">
-        <v>6239470</v>
+        <v>6239523</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,24 +764,9 @@
           <t>2025-03-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flög upp från träd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +781,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -805,7 +796,7 @@
         <v>123445741</v>
       </c>
       <c r="B3" t="n">
-        <v>57857</v>
+        <v>57860</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -904,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123445745</v>
+        <v>123445744</v>
       </c>
       <c r="B4" t="n">
-        <v>57638</v>
+        <v>58168</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,20 +907,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -937,33 +928,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>410992</v>
+        <v>411000</v>
       </c>
       <c r="R4" t="n">
-        <v>6239484</v>
+        <v>6239530</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1025,7 +1000,7 @@
         <v>123425822</v>
       </c>
       <c r="B5" t="n">
-        <v>57857</v>
+        <v>57860</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1134,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123426658</v>
+        <v>123445737</v>
       </c>
       <c r="B6" t="n">
-        <v>57640</v>
+        <v>57643</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,25 +1142,36 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tidemanstorp, Tidemanstorp, Sk</t>
+          <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>410969</v>
+        <v>411017</v>
       </c>
       <c r="R6" t="n">
-        <v>6239507</v>
+        <v>6239474</v>
       </c>
       <c r="S6" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,19 +1198,9 @@
           <t>2025-03-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,22 +1215,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123445735</v>
+        <v>123445745</v>
       </c>
       <c r="B7" t="n">
-        <v>57640</v>
+        <v>57641</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,21 +1243,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1307,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>411027</v>
+        <v>410992</v>
       </c>
       <c r="R7" t="n">
-        <v>6239523</v>
+        <v>6239484</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1369,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123445744</v>
+        <v>123427756</v>
       </c>
       <c r="B8" t="n">
-        <v>58165</v>
+        <v>56700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,37 +1361,47 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103044</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fäje myr norr, Sk</t>
+          <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>411000</v>
+        <v>410821</v>
       </c>
       <c r="R8" t="n">
-        <v>6239530</v>
+        <v>6239470</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1442,9 +1428,24 @@
           <t>2025-03-24</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Flög upp från träd</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,22 +1460,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123445737</v>
+        <v>123426658</v>
       </c>
       <c r="B9" t="n">
-        <v>57640</v>
+        <v>57643</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,36 +1505,25 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fäje myr norr, Sk</t>
+          <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>411017</v>
+        <v>410969</v>
       </c>
       <c r="R9" t="n">
-        <v>6239474</v>
+        <v>6239507</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1560,9 +1550,19 @@
           <t>2025-03-24</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,12 +1577,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 4615-2025 artfynd.xlsx
+++ b/artfynd/A 4615-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123445735</v>
+        <v>123445741</v>
       </c>
       <c r="B2" t="n">
-        <v>57643</v>
+        <v>57861</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,54 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>411027</v>
+        <v>410991</v>
       </c>
       <c r="R2" t="n">
-        <v>6239523</v>
+        <v>6239508</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -793,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123445741</v>
+        <v>123425822</v>
       </c>
       <c r="B3" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fäje myr norr, Sk</t>
+          <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>410991</v>
+        <v>410977</v>
       </c>
       <c r="R3" t="n">
-        <v>6239508</v>
+        <v>6239502</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,9 +850,19 @@
           <t>2025-03-24</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123445744</v>
+        <v>123445737</v>
       </c>
       <c r="B4" t="n">
-        <v>58168</v>
+        <v>57644</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,38 +901,54 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>411000</v>
+        <v>411017</v>
       </c>
       <c r="R4" t="n">
-        <v>6239530</v>
+        <v>6239474</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -997,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123425822</v>
+        <v>123426658</v>
       </c>
       <c r="B5" t="n">
-        <v>57860</v>
+        <v>57644</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,41 +1019,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>410977</v>
+        <v>410969</v>
       </c>
       <c r="R5" t="n">
-        <v>6239502</v>
+        <v>6239507</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1072,7 +1087,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1082,7 +1097,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123445737</v>
+        <v>123445735</v>
       </c>
       <c r="B6" t="n">
-        <v>57643</v>
+        <v>57644</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>411017</v>
+        <v>411027</v>
       </c>
       <c r="R6" t="n">
-        <v>6239474</v>
+        <v>6239523</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1230,7 +1245,7 @@
         <v>123445745</v>
       </c>
       <c r="B7" t="n">
-        <v>57641</v>
+        <v>57642</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1345,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123427756</v>
+        <v>123445744</v>
       </c>
       <c r="B8" t="n">
-        <v>56700</v>
+        <v>58169</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1361,47 +1376,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tidemanstorp, Tidemanstorp, Sk</t>
+          <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>410821</v>
+        <v>411000</v>
       </c>
       <c r="R8" t="n">
-        <v>6239470</v>
+        <v>6239530</v>
       </c>
       <c r="S8" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1428,24 +1433,9 @@
           <t>2025-03-24</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Flög upp från träd</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,22 +1450,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123426658</v>
+        <v>123427756</v>
       </c>
       <c r="B9" t="n">
-        <v>57643</v>
+        <v>56700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,31 +1474,36 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1517,10 +1512,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>410969</v>
+        <v>410821</v>
       </c>
       <c r="R9" t="n">
-        <v>6239507</v>
+        <v>6239470</v>
       </c>
       <c r="S9" t="n">
         <v>30</v>
@@ -1552,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,7 +1557,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Flög upp från träd</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 4615-2025 artfynd.xlsx
+++ b/artfynd/A 4615-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123445741</v>
+        <v>123426658</v>
       </c>
       <c r="B2" t="n">
-        <v>57861</v>
+        <v>57644</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fäje myr norr, Sk</t>
+          <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>410991</v>
+        <v>410969</v>
       </c>
       <c r="R2" t="n">
-        <v>6239508</v>
+        <v>6239507</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,9 +753,19 @@
           <t>2025-03-24</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,12 +780,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -889,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123445737</v>
+        <v>123445744</v>
       </c>
       <c r="B4" t="n">
-        <v>57644</v>
+        <v>58169</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,54 +916,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>411017</v>
+        <v>411000</v>
       </c>
       <c r="R4" t="n">
-        <v>6239474</v>
+        <v>6239530</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1007,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123426658</v>
+        <v>123445745</v>
       </c>
       <c r="B5" t="n">
-        <v>57644</v>
+        <v>57642</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,42 +1022,53 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tidemanstorp, Tidemanstorp, Sk</t>
+          <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>410969</v>
+        <v>410992</v>
       </c>
       <c r="R5" t="n">
-        <v>6239507</v>
+        <v>6239484</v>
       </c>
       <c r="S5" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,19 +1095,9 @@
           <t>2025-03-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,19 +1112,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123445735</v>
+        <v>123445737</v>
       </c>
       <c r="B6" t="n">
         <v>57644</v>
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>411027</v>
+        <v>411017</v>
       </c>
       <c r="R6" t="n">
-        <v>6239523</v>
+        <v>6239474</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1242,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123445745</v>
+        <v>123445741</v>
       </c>
       <c r="B7" t="n">
-        <v>57642</v>
+        <v>57861</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,20 +1254,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1275,33 +1275,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>410992</v>
+        <v>410991</v>
       </c>
       <c r="R7" t="n">
-        <v>6239484</v>
+        <v>6239508</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1360,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123445744</v>
+        <v>123427756</v>
       </c>
       <c r="B8" t="n">
-        <v>58169</v>
+        <v>56700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,37 +1360,47 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103044</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fäje myr norr, Sk</t>
+          <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>411000</v>
+        <v>410821</v>
       </c>
       <c r="R8" t="n">
-        <v>6239530</v>
+        <v>6239470</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1433,9 +1427,24 @@
           <t>2025-03-24</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Flög upp från träd</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,22 +1459,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123427756</v>
+        <v>123445735</v>
       </c>
       <c r="B9" t="n">
-        <v>56700</v>
+        <v>57644</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1474,51 +1483,57 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>rastande</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tidemanstorp, Tidemanstorp, Sk</t>
+          <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>410821</v>
+        <v>411027</v>
       </c>
       <c r="R9" t="n">
-        <v>6239470</v>
+        <v>6239523</v>
       </c>
       <c r="S9" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1545,24 +1560,9 @@
           <t>2025-03-24</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Flög upp från träd</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,12 +1577,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 4615-2025 artfynd.xlsx
+++ b/artfynd/A 4615-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123426658</v>
+        <v>123425822</v>
       </c>
       <c r="B2" t="n">
-        <v>57644</v>
+        <v>57861</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>410969</v>
+        <v>410977</v>
       </c>
       <c r="R2" t="n">
-        <v>6239507</v>
+        <v>6239502</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123425822</v>
+        <v>123445741</v>
       </c>
       <c r="B3" t="n">
         <v>57861</v>
@@ -828,17 +823,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tidemanstorp, Tidemanstorp, Sk</t>
+          <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>410977</v>
+        <v>410991</v>
       </c>
       <c r="R3" t="n">
-        <v>6239502</v>
+        <v>6239508</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,19 +860,9 @@
           <t>2025-03-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123445744</v>
+        <v>123426658</v>
       </c>
       <c r="B4" t="n">
-        <v>58169</v>
+        <v>57644</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,41 +901,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fäje myr norr, Sk</t>
+          <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>411000</v>
+        <v>410969</v>
       </c>
       <c r="R4" t="n">
-        <v>6239530</v>
+        <v>6239507</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,9 +967,19 @@
           <t>2025-03-24</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,22 +994,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123445745</v>
+        <v>123427756</v>
       </c>
       <c r="B5" t="n">
-        <v>57642</v>
+        <v>56700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,57 +1018,51 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fäje myr norr, Sk</t>
+          <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>410992</v>
+        <v>410821</v>
       </c>
       <c r="R5" t="n">
-        <v>6239484</v>
+        <v>6239470</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,9 +1089,24 @@
           <t>2025-03-24</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Flög upp från träd</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,22 +1121,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123445737</v>
+        <v>123445744</v>
       </c>
       <c r="B6" t="n">
-        <v>57644</v>
+        <v>58169</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,54 +1145,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>103044</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>411017</v>
+        <v>411000</v>
       </c>
       <c r="R6" t="n">
-        <v>6239474</v>
+        <v>6239530</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1242,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123445741</v>
+        <v>123445735</v>
       </c>
       <c r="B7" t="n">
-        <v>57861</v>
+        <v>57644</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,38 +1247,54 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>410991</v>
+        <v>411027</v>
       </c>
       <c r="R7" t="n">
-        <v>6239508</v>
+        <v>6239523</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1344,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123427756</v>
+        <v>123445745</v>
       </c>
       <c r="B8" t="n">
-        <v>56700</v>
+        <v>57642</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,51 +1365,57 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>103020</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>rastande</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tidemanstorp, Tidemanstorp, Sk</t>
+          <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>410821</v>
+        <v>410992</v>
       </c>
       <c r="R8" t="n">
-        <v>6239470</v>
+        <v>6239484</v>
       </c>
       <c r="S8" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,24 +1442,9 @@
           <t>2025-03-24</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Flög upp från träd</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,19 +1459,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123445735</v>
+        <v>123445737</v>
       </c>
       <c r="B9" t="n">
         <v>57644</v>
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>411027</v>
+        <v>411017</v>
       </c>
       <c r="R9" t="n">
-        <v>6239523</v>
+        <v>6239474</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 4615-2025 artfynd.xlsx
+++ b/artfynd/A 4615-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123425822</v>
+        <v>123445741</v>
       </c>
       <c r="B2" t="n">
         <v>57861</v>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tidemanstorp, Tidemanstorp, Sk</t>
+          <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>410977</v>
+        <v>410991</v>
       </c>
       <c r="R2" t="n">
-        <v>6239502</v>
+        <v>6239508</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +748,9 @@
           <t>2025-03-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123445741</v>
+        <v>123426658</v>
       </c>
       <c r="B3" t="n">
-        <v>57861</v>
+        <v>57644</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,41 +789,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fäje myr norr, Sk</t>
+          <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>410991</v>
+        <v>410969</v>
       </c>
       <c r="R3" t="n">
-        <v>6239508</v>
+        <v>6239507</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,9 +855,19 @@
           <t>2025-03-24</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +882,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123426658</v>
+        <v>123427756</v>
       </c>
       <c r="B4" t="n">
-        <v>57644</v>
+        <v>56700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,31 +906,36 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -934,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>410969</v>
+        <v>410821</v>
       </c>
       <c r="R4" t="n">
-        <v>6239507</v>
+        <v>6239470</v>
       </c>
       <c r="S4" t="n">
         <v>30</v>
@@ -969,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flög upp från träd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123427756</v>
+        <v>123425822</v>
       </c>
       <c r="B5" t="n">
-        <v>56700</v>
+        <v>57861</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,47 +1037,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>410821</v>
+        <v>410977</v>
       </c>
       <c r="R5" t="n">
-        <v>6239470</v>
+        <v>6239502</v>
       </c>
       <c r="S5" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,12 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flög upp från träd</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1353,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123445745</v>
+        <v>123445737</v>
       </c>
       <c r="B8" t="n">
-        <v>57642</v>
+        <v>57644</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,21 +1369,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>410992</v>
+        <v>411017</v>
       </c>
       <c r="R8" t="n">
-        <v>6239484</v>
+        <v>6239474</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123445737</v>
+        <v>123445745</v>
       </c>
       <c r="B9" t="n">
-        <v>57644</v>
+        <v>57642</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>411017</v>
+        <v>410992</v>
       </c>
       <c r="R9" t="n">
-        <v>6239474</v>
+        <v>6239484</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 4615-2025 artfynd.xlsx
+++ b/artfynd/A 4615-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123445741</v>
+        <v>123426658</v>
       </c>
       <c r="B2" t="n">
-        <v>57861</v>
+        <v>57644</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fäje myr norr, Sk</t>
+          <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>410991</v>
+        <v>410969</v>
       </c>
       <c r="R2" t="n">
-        <v>6239508</v>
+        <v>6239507</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,9 +753,19 @@
           <t>2025-03-24</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123426658</v>
+        <v>123425822</v>
       </c>
       <c r="B3" t="n">
-        <v>57644</v>
+        <v>57861</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,46 +804,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>410969</v>
+        <v>410977</v>
       </c>
       <c r="R3" t="n">
-        <v>6239507</v>
+        <v>6239502</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123427756</v>
+        <v>123445741</v>
       </c>
       <c r="B4" t="n">
-        <v>56700</v>
+        <v>57861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,47 +920,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tidemanstorp, Tidemanstorp, Sk</t>
+          <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>410821</v>
+        <v>410991</v>
       </c>
       <c r="R4" t="n">
-        <v>6239470</v>
+        <v>6239508</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,24 +977,9 @@
           <t>2025-03-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flög upp från träd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +994,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123425822</v>
+        <v>123427756</v>
       </c>
       <c r="B5" t="n">
-        <v>57861</v>
+        <v>56700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,37 +1022,47 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>410977</v>
+        <v>410821</v>
       </c>
       <c r="R5" t="n">
-        <v>6239502</v>
+        <v>6239470</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1101,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Flög upp från träd</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123445744</v>
+        <v>123445735</v>
       </c>
       <c r="B6" t="n">
-        <v>58169</v>
+        <v>57644</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,38 +1145,54 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>411000</v>
+        <v>411027</v>
       </c>
       <c r="R6" t="n">
-        <v>6239530</v>
+        <v>6239523</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1235,7 +1251,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123445735</v>
+        <v>123445737</v>
       </c>
       <c r="B7" t="n">
         <v>57644</v>
@@ -1291,10 +1307,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>411027</v>
+        <v>411017</v>
       </c>
       <c r="R7" t="n">
-        <v>6239523</v>
+        <v>6239474</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1353,10 +1369,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123445737</v>
+        <v>123445745</v>
       </c>
       <c r="B8" t="n">
-        <v>57644</v>
+        <v>57642</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,21 +1385,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1409,10 +1425,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>411017</v>
+        <v>410992</v>
       </c>
       <c r="R8" t="n">
-        <v>6239474</v>
+        <v>6239484</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1471,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123445745</v>
+        <v>123445744</v>
       </c>
       <c r="B9" t="n">
-        <v>57642</v>
+        <v>58169</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1483,20 +1499,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103020</v>
+        <v>103044</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1504,33 +1520,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>410992</v>
+        <v>411000</v>
       </c>
       <c r="R9" t="n">
-        <v>6239484</v>
+        <v>6239530</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 4615-2025 artfynd.xlsx
+++ b/artfynd/A 4615-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123445744</v>
+        <v>123427756</v>
       </c>
       <c r="B2" t="n">
-        <v>58191</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,47 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fäje myr norr, Sk</t>
+          <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>411000</v>
+        <v>410821</v>
       </c>
       <c r="R2" t="n">
-        <v>6239530</v>
+        <v>6239470</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,9 +753,24 @@
           <t>2025-03-24</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flög upp från träd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,49 +785,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123445745</v>
+        <v>123445734</v>
       </c>
       <c r="B3" t="n">
-        <v>57664</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +835,14 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -833,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>410992</v>
+        <v>410871</v>
       </c>
       <c r="R3" t="n">
-        <v>6239484</v>
+        <v>6239503</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -895,69 +914,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123445737</v>
+        <v>123425822</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fäje myr norr, Sk</t>
+          <t>Tidemanstorp, Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>411017</v>
+        <v>410977</v>
       </c>
       <c r="R4" t="n">
-        <v>6239474</v>
+        <v>6239502</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,9 +982,19 @@
           <t>2025-03-24</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,12 +1009,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1016,12 +1024,7 @@
         <v>123445741</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,15 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123425822</v>
+        <v>133467997</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,20 +1146,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tidemanstorp, Tidemanstorp, Sk</t>
+          <t>Tidemanstorp, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>410977</v>
+        <v>410904</v>
       </c>
       <c r="R6" t="n">
-        <v>6239502</v>
+        <v>6239476</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,22 +1191,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,15 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123445735</v>
+        <v>123445745</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1243,21 +1244,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1283,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>411027</v>
+        <v>410992</v>
       </c>
       <c r="R7" t="n">
-        <v>6239523</v>
+        <v>6239484</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1348,12 +1349,7 @@
         <v>123426658</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,63 +1458,64 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123427756</v>
+        <v>123445735</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>rastande</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tidemanstorp, Tidemanstorp, Sk</t>
+          <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>410821</v>
+        <v>411027</v>
       </c>
       <c r="R9" t="n">
-        <v>6239470</v>
+        <v>6239523</v>
       </c>
       <c r="S9" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1545,24 +1542,9 @@
           <t>2025-03-24</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Flög upp från träd</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,44 +1559,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133467997</v>
+        <v>123445737</v>
       </c>
       <c r="B10" t="n">
-        <v>58349</v>
+        <v>58114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1622,23 +1604,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tidemanstorp, Sk</t>
+          <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>410904</v>
+        <v>411017</v>
       </c>
       <c r="R10" t="n">
-        <v>6239476</v>
+        <v>6239474</v>
       </c>
       <c r="S10" t="n">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1662,22 +1652,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:49</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,15 +1672,112 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123445744</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Fäje myr norr, Sk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>411000</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6239530</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vittsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Thomas Arnström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Thomas Arnström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4615-2025 artfynd.xlsx
+++ b/artfynd/A 4615-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123427756</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,6 +921,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123445734</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1018,6 +1033,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123425822</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123445741</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1230,6 +1255,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133467997</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,6 +1373,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123445745</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1455,6 +1490,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123426658</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1568,6 +1608,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123445735</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1681,6 +1726,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123445737</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1778,8 +1828,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123445744</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>